--- a/tests/fixtures/banks/woori_sample.xlsx
+++ b/tests/fixtures/banks/woori_sample.xlsx
@@ -419,266 +419,268 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>우리은행 계좌 거래내역</t>
+          <t>최근거래내역조회</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>계좌번호: 1002-123-456789</t>
+          <t>계좌번호 : 1006-001-539600</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>조회기간: 2026.01.01 ~ 2026.01.31</t>
+          <t>조회기간 : 2026.01.01 ~ 2026.01.31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>거래일자</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>거래일시</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>적요</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>기재내용</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>지급(원)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>입금(원)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>잔액(원)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>거래점</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>거래처</t>
+          <t>거래후 잔액(원)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>취급점</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>거래번호</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>소모품구입</t>
+          <t>2026-01-01 10:00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>85000</t>
+          <t>펌뱅킹</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>기재내용</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>3200000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>5000000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>서초지점</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WR000001</t>
+          <t>급여</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
+      <c r="A6" t="n">
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>2026-01-02 10:00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>펌뱅킹</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>기재내용</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>150000</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>5000000</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>서초지점</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WR000002</t>
+          <t>보험료</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
+      <c r="A7" t="n">
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>외상매출금회수</t>
+          <t>2026-01-03 10:00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>펌뱅킹</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>기재내용</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>5000000</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>서초지점</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>고객사B</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>WR000003</t>
+          <t>컨설팅 비용 지출</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01-04</t>
-        </is>
+      <c r="A8" t="n">
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>세금과공과</t>
+          <t>2026-01-04 10:00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>550000</t>
+          <t>펌뱅킹</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+          <t>기재내용</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>5000000</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>서초지점</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>국세청</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>WR000004</t>
+          <t>알앤디 자금 입금</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
+      <c r="A9" t="n">
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>알수없음ZZZ</t>
+          <t>2026-01-05 10:00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>펌뱅킹</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>기재내용</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>1000000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>5000000</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>서초지점</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>WR000005</t>
+          <t>자계좌 이체</t>
         </is>
       </c>
     </row>
